--- a/Scripts_inesdattatreya/data_output/inesdattatreya_G2_riskp_dist_2510.xlsx
+++ b/Scripts_inesdattatreya/data_output/inesdattatreya_G2_riskp_dist_2510.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>lca_class</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2916,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="AG32">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="AG34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="AG35">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -4180,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="AG36">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4271,6 +4271,9 @@
       <c r="AF37">
         <v>0</v>
       </c>
+      <c r="AG37">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4373,6 +4376,9 @@
       <c r="AF38">
         <v>0</v>
       </c>
+      <c r="AG38">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4475,6 +4481,9 @@
       <c r="AF39">
         <v>0</v>
       </c>
+      <c r="AG39">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4577,6 +4586,9 @@
       <c r="AF40">
         <v>0</v>
       </c>
+      <c r="AG40">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4679,6 +4691,9 @@
       <c r="AF41">
         <v>0</v>
       </c>
+      <c r="AG41">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4768,6 +4783,9 @@
       <c r="AF42">
         <v>0</v>
       </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4870,6 +4888,9 @@
       <c r="AF43">
         <v>0</v>
       </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4972,6 +4993,9 @@
       <c r="AF44">
         <v>0</v>
       </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5071,6 +5095,9 @@
       <c r="AF45">
         <v>0</v>
       </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5170,6 +5197,9 @@
       <c r="AF46">
         <v>0</v>
       </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5260,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -5362,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -5467,7 +5497,7 @@
         <v>0</v>
       </c>
       <c r="AG49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -5569,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -5680,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -5772,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="AG52">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -5883,7 +5913,7 @@
         <v>0</v>
       </c>
       <c r="AG53">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -5994,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="AG54">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -6099,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="AG55">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -6204,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AG56">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -6296,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="AG57">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -6407,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="AG58">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -6512,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="AG59">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -6623,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="AG60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -6728,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="AG61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -6819,6 +6849,9 @@
       <c r="AF62">
         <v>0</v>
       </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6921,6 +6954,9 @@
       <c r="AF63">
         <v>0</v>
       </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7023,6 +7059,9 @@
       <c r="AF64">
         <v>0</v>
       </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7125,6 +7164,9 @@
       <c r="AF65">
         <v>0</v>
       </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7227,6 +7269,9 @@
       <c r="AF66">
         <v>0</v>
       </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7317,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -7428,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="AG68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -7539,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="AG69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -7644,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -7749,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="AG71">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -8359,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="AG77">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8461,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="AG78">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8563,7 +8608,7 @@
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -8665,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="AG80">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8776,7 +8821,7 @@
         <v>0</v>
       </c>
       <c r="AG81">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -8868,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="AG82">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -8979,7 +9024,7 @@
         <v>0</v>
       </c>
       <c r="AG83">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -9084,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="AG84">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -9195,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="AG85">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -9300,7 +9345,7 @@
         <v>0</v>
       </c>
       <c r="AG86">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -9392,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="AG87">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -9503,7 +9548,7 @@
         <v>0</v>
       </c>
       <c r="AG88">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -9614,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="AG89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -9719,7 +9764,7 @@
         <v>0</v>
       </c>
       <c r="AG90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -9824,7 +9869,7 @@
         <v>0</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -9915,6 +9960,9 @@
       <c r="AF92">
         <v>0</v>
       </c>
+      <c r="AG92">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10014,6 +10062,9 @@
       <c r="AF93">
         <v>0</v>
       </c>
+      <c r="AG93">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10113,6 +10164,9 @@
       <c r="AF94">
         <v>0</v>
       </c>
+      <c r="AG94">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10215,6 +10269,9 @@
       <c r="AF95">
         <v>0</v>
       </c>
+      <c r="AG95">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10314,6 +10371,9 @@
       <c r="AF96">
         <v>0</v>
       </c>
+      <c r="AG96">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10928,7 +10988,7 @@
         <v>0</v>
       </c>
       <c r="AG102">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -11039,7 +11099,7 @@
         <v>0</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -11150,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="AG104">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -11261,7 +11321,7 @@
         <v>0</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -11366,7 +11426,7 @@
         <v>0</v>
       </c>
       <c r="AG106">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -11458,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="AG107">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -11563,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="AG108">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -11674,7 +11734,7 @@
         <v>0</v>
       </c>
       <c r="AG109">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -11779,7 +11839,7 @@
         <v>0</v>
       </c>
       <c r="AG110">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -11884,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="AG111">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -12500,7 +12560,7 @@
         <v>0</v>
       </c>
       <c r="AG117">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -12611,7 +12671,7 @@
         <v>0</v>
       </c>
       <c r="AG118">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -12716,7 +12776,7 @@
         <v>0</v>
       </c>
       <c r="AG119">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -12827,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="AG120">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -12938,7 +12998,7 @@
         <v>0</v>
       </c>
       <c r="AG121">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
